--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8938-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8938-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB7794AD-24E4-4AEB-B90E-4BC2C427A374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8AD1E81-514E-4021-9141-05727631367E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{ED14FF23-ACBE-4D00-81F4-9D3FCD50A39E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C085C386-6F58-4DDC-980D-97F90099406D}"/>
   </bookViews>
   <sheets>
     <sheet name="8938-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,24 +1400,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DB278-D4D5-49C5-8E83-8205802A7A75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECC02D2-2D32-4ED7-B566-50E949AC9E79}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1445,7 +1445,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1475,7 +1475,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1571,7 +1571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2010</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>2009</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>2008</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
         <v>2007</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>2006</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>2005</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>2004</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="34">
         <v>2003</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>2002</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="34">
         <v>2001</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>2000</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>25</v>
       </c>
